--- a/logs/experiments_systematic/after_analysing_features/after_analysing_features.xlsx
+++ b/logs/experiments_systematic/after_analysing_features/after_analysing_features.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgep-my.sharepoint.com/personal/uxue_ballarin_alumni_mondragon_edu/Documents/Semestre 8-Erasmus/Simula/ship_qnn/logs/experiments_systematic/after_analysing_features/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="11_25DDD2B7D3105479BBB92F11595ED87656CE1E8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{603E4EED-9E04-4A16-8DF8-FCA4519BB042}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="11_25DDD2B7D3105479BBB92F11595ED87656CE1E8D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9C705D8-8EB7-4DEB-993B-79ACA74E0A60}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1812" yWindow="1812" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId3"/>
+    <pivotCache cacheId="4" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="213">
   <si>
     <t>date</t>
   </si>
@@ -757,7 +757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -770,12 +770,135 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="11">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF006100"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="65"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <left style="medium">
@@ -963,9 +1086,7 @@
       <sharedItems/>
     </cacheField>
     <cacheField name="reps" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1" count="1">
-        <n v="1"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="1"/>
     </cacheField>
     <cacheField name="map" numFmtId="0">
       <sharedItems count="5">
@@ -1168,7 +1289,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1246,7 +1367,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1324,7 +1445,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1402,7 +1523,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1480,7 +1601,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1558,7 +1679,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1636,7 +1757,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1714,7 +1835,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1792,7 +1913,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1870,7 +1991,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -1948,7 +2069,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2026,7 +2147,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2104,7 +2225,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2182,7 +2303,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2260,7 +2381,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2338,7 +2459,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2416,7 +2537,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2494,7 +2615,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2572,7 +2693,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2650,7 +2771,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2728,7 +2849,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2806,7 +2927,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2884,7 +3005,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -2962,7 +3083,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3040,7 +3161,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3118,7 +3239,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3196,7 +3317,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3274,7 +3395,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3352,7 +3473,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3430,7 +3551,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3508,7 +3629,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3586,7 +3707,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3664,7 +3785,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3742,7 +3863,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3820,7 +3941,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3898,7 +4019,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -3976,7 +4097,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4054,7 +4175,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4132,7 +4253,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4210,7 +4331,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4288,7 +4409,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4366,7 +4487,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4444,7 +4565,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4522,7 +4643,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4600,7 +4721,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4678,7 +4799,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="4"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4756,7 +4877,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="0"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4834,7 +4955,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="2"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4912,7 +5033,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="1"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -4990,7 +5111,7 @@
     <s v="serial"/>
     <s v="effsu2"/>
     <s v="lin"/>
-    <x v="0"/>
+    <n v="1"/>
     <x v="3"/>
     <b v="0"/>
     <s v="spsa"/>
@@ -5050,8 +5171,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9096C394-E2A9-4483-A1AA-685A07651176}" name="TablaDinámica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:L12" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9096C394-E2A9-4483-A1AA-685A07651176}" name="TablaDinámica1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:L13" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="76">
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
@@ -5077,7 +5198,7 @@
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
         <item sd="0" x="0"/>
-        <item sd="0" x="4"/>
+        <item x="4"/>
         <item sd="0" x="2"/>
         <item sd="0" x="3"/>
         <item sd="0" x="1"/>
@@ -5104,12 +5225,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="2">
-        <item sd="0" x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
         <item sd="0" x="3"/>
@@ -5174,14 +5290,13 @@
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
   </pivotFields>
-  <rowFields count="5">
+  <rowFields count="4">
     <field x="17"/>
     <field x="7"/>
     <field x="22"/>
-    <field x="21"/>
     <field x="2"/>
   </rowFields>
-  <rowItems count="9">
+  <rowItems count="10">
     <i>
       <x/>
     </i>
@@ -5205,6 +5320,9 @@
     </i>
     <i r="1">
       <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
     </i>
     <i t="grand">
       <x/>
@@ -5262,7 +5380,7 @@
     <dataField name="Promedio de Yaw Angle Global closed R2" fld="75" subtotal="average" baseField="22" baseItem="0"/>
   </dataFields>
   <formats count="2">
-    <format dxfId="1">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -5277,7 +5395,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="6">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="4294967294" count="1" selected="0">
@@ -5306,7 +5424,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{216F7486-0139-4AA7-9160-B04561EEE3EA}" name="Tabla1" displayName="Tabla1" ref="A1:BX51" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{216F7486-0139-4AA7-9160-B04561EEE3EA}" name="Tabla1" displayName="Tabla1" ref="A1:BX51" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
   <autoFilter ref="A1:BX51" xr:uid="{216F7486-0139-4AA7-9160-B04561EEE3EA}"/>
   <tableColumns count="76">
     <tableColumn id="1" xr3:uid="{79DFB838-DDA6-48FC-9B9E-B5EA9B1C9BC7}" name="date"/>
@@ -17334,7 +17452,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF582669-FFBF-408F-BF9D-034E327A9A2C}">
-  <dimension ref="A3:L23"/>
+  <dimension ref="A3:L13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="47" bestFit="1" customWidth="1"/>
@@ -17662,7 +17780,7 @@
       <c r="B11" s="5">
         <v>10</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="7">
         <v>0.93436868131083983</v>
       </c>
       <c r="D11" s="5">
@@ -17694,45 +17812,81 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="5">
+        <v>10</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.93436868131083983</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.94098523663345612</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0.94340582890391711</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.92224098374634345</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.93084267595964243</v>
+      </c>
+      <c r="H12" s="5">
+        <v>-0.84635344168980498</v>
+      </c>
+      <c r="I12" s="5">
+        <v>-1.6587844510604088</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0.13411707024764968</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0.87516763174436285</v>
+      </c>
+      <c r="L12" s="5">
+        <v>-2.7359140176908263</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B13" s="5">
         <v>50</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C13" s="5">
         <v>0.90115571456018728</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D13" s="5">
         <v>0.93942618602206318</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E13" s="5">
         <v>0.90827512099417329</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F13" s="5">
         <v>0.87823506677487306</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G13" s="5">
         <v>0.87868648444963826</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H13" s="5">
         <v>-1.0097760256791675</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I13" s="5">
         <v>-2.8519639039039202</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J13" s="5">
         <v>0.15910983234331819</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K13" s="5">
         <v>0.3092996763863779</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L13" s="5">
         <v>-1.6555497075424472</v>
       </c>
     </row>
-    <row r="22" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="23" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <conditionalFormatting sqref="C3:L3">
     <cfRule type="colorScale" priority="1">
